--- a/data/xlsx/audit_amessefe_v2.xlsx
+++ b/data/xlsx/audit_amessefe_v2.xlsx
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC2" t="b">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -777,7 +777,7 @@
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC3" t="b">
         <v>0</v>
@@ -808,17 +808,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
@@ -827,7 +827,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
@@ -909,11 +909,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S5" t="b">
         <v>1</v>
@@ -958,7 +958,7 @@
         <v>3</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="b">
         <v>1</v>
@@ -979,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="b">
         <v>1</v>
@@ -988,7 +988,7 @@
         <v>3</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -1029,7 +1029,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S6" t="b">
         <v>1</v>
@@ -1059,7 +1059,7 @@
         <v>3</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
@@ -1080,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC6" t="b">
         <v>1</v>
@@ -1089,7 +1089,7 @@
         <v>3</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1121,7 +1121,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC7" t="b">
         <v>0</v>
@@ -1222,7 +1222,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC8" t="b">
         <v>0</v>
@@ -1313,11 +1313,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S9" t="b">
         <v>1</v>
@@ -1362,7 +1362,7 @@
         <v>3</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="b">
         <v>0</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1424,7 +1424,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -1454,7 +1454,7 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S10" t="b">
         <v>1</v>
@@ -1463,7 +1463,7 @@
         <v>3</v>
       </c>
       <c r="U10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
@@ -1484,7 +1484,7 @@
         <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC10" t="b">
         <v>0</v>
@@ -1515,17 +1515,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -1534,7 +1534,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -1555,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S11" t="b">
         <v>1</v>
@@ -1564,7 +1564,7 @@
         <v>3</v>
       </c>
       <c r="U11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
@@ -1585,7 +1585,7 @@
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC11" t="b">
         <v>1</v>
@@ -1594,7 +1594,7 @@
         <v>3</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1626,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -1686,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC12" t="b">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1727,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S13" t="b">
         <v>1</v>
@@ -1766,7 +1766,7 @@
         <v>3</v>
       </c>
       <c r="U13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="b">
         <v>1</v>
@@ -1787,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="b">
         <v>0</v>
@@ -1818,17 +1818,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -1837,7 +1837,7 @@
         <v>3</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -1858,7 +1858,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S14" t="b">
         <v>1</v>
@@ -1867,7 +1867,7 @@
         <v>3</v>
       </c>
       <c r="U14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
@@ -1888,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="b">
         <v>1</v>
@@ -1897,7 +1897,7 @@
         <v>3</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1929,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -1989,7 +1989,7 @@
         <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC15" t="b">
         <v>0</v>
@@ -2030,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -2090,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC16" t="b">
         <v>0</v>
@@ -2121,17 +2121,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -2140,7 +2140,7 @@
         <v>3</v>
       </c>
       <c r="K17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -2161,7 +2161,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S17" t="b">
         <v>1</v>
@@ -2170,7 +2170,7 @@
         <v>3</v>
       </c>
       <c r="U17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
@@ -2191,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC17" t="b">
         <v>1</v>
@@ -2200,7 +2200,7 @@
         <v>3</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -2232,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
@@ -2262,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S18" t="b">
         <v>1</v>
@@ -2271,7 +2271,7 @@
         <v>3</v>
       </c>
       <c r="U18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="b">
         <v>1</v>
@@ -2292,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC18" t="b">
         <v>0</v>
@@ -2333,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -2393,7 +2393,7 @@
         <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC19" t="b">
         <v>0</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -2434,7 +2434,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -2464,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S20" t="b">
         <v>1</v>
@@ -2473,7 +2473,7 @@
         <v>3</v>
       </c>
       <c r="U20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="b">
         <v>1</v>
@@ -2494,7 +2494,7 @@
         <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC20" t="b">
         <v>0</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2535,7 +2535,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -2565,7 +2565,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S21" t="b">
         <v>1</v>
@@ -2574,7 +2574,7 @@
         <v>3</v>
       </c>
       <c r="U21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
@@ -2595,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC21" t="b">
         <v>0</v>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -2636,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -2666,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S22" t="b">
         <v>1</v>
@@ -2675,7 +2675,7 @@
         <v>3</v>
       </c>
       <c r="U22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" t="b">
         <v>1</v>
@@ -2696,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC22" t="b">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -2797,7 +2797,7 @@
         <v>1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC23" t="b">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -2898,7 +2898,7 @@
         <v>1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC24" t="b">
         <v>0</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2939,7 +2939,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S25" t="b">
         <v>1</v>
@@ -2978,7 +2978,7 @@
         <v>3</v>
       </c>
       <c r="U25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" t="b">
         <v>1</v>
@@ -2999,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC25" t="b">
         <v>0</v>
@@ -3040,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -3100,7 +3100,7 @@
         <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC26" t="b">
         <v>0</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -3141,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -3171,7 +3171,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S27" t="b">
         <v>1</v>
@@ -3180,7 +3180,7 @@
         <v>3</v>
       </c>
       <c r="U27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="b">
         <v>1</v>
@@ -3201,7 +3201,7 @@
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC27" t="b">
         <v>0</v>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -3242,7 +3242,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -3272,7 +3272,7 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S28" t="b">
         <v>1</v>
@@ -3281,7 +3281,7 @@
         <v>3</v>
       </c>
       <c r="U28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="b">
         <v>1</v>
@@ -3302,7 +3302,7 @@
         <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC28" t="b">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -3504,7 +3504,7 @@
         <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC30" t="b">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -3605,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC31" t="b">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -3706,7 +3706,7 @@
         <v>1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC32" t="b">
         <v>0</v>
@@ -3747,7 +3747,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -3878,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S34" t="b">
         <v>1</v>
@@ -3887,7 +3887,7 @@
         <v>3</v>
       </c>
       <c r="U34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="b">
         <v>1</v>
@@ -3908,7 +3908,7 @@
         <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC34" t="b">
         <v>0</v>
@@ -3939,17 +3939,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I35" t="b">
         <v>1</v>
@@ -3958,7 +3958,7 @@
         <v>3</v>
       </c>
       <c r="K35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="b">
         <v>1</v>
@@ -3979,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S35" t="b">
         <v>1</v>
@@ -3988,7 +3988,7 @@
         <v>3</v>
       </c>
       <c r="U35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" t="b">
         <v>1</v>
@@ -4009,7 +4009,7 @@
         <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC35" t="b">
         <v>1</v>
@@ -4018,7 +4018,7 @@
         <v>3</v>
       </c>
       <c r="AE35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4040,17 +4040,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -4059,7 +4059,7 @@
         <v>3</v>
       </c>
       <c r="K36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
@@ -4080,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S36" t="b">
         <v>1</v>
@@ -4089,7 +4089,7 @@
         <v>3</v>
       </c>
       <c r="U36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC36" t="b">
         <v>1</v>
@@ -4119,7 +4119,7 @@
         <v>3</v>
       </c>
       <c r="AE36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4141,17 +4141,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
@@ -4160,7 +4160,7 @@
         <v>3</v>
       </c>
       <c r="K37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
@@ -4181,7 +4181,7 @@
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S37" t="b">
         <v>1</v>
@@ -4190,7 +4190,7 @@
         <v>3</v>
       </c>
       <c r="U37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" t="b">
         <v>1</v>
@@ -4211,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC37" t="b">
         <v>1</v>
@@ -4220,7 +4220,7 @@
         <v>3</v>
       </c>
       <c r="AE37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4242,17 +4242,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -4261,7 +4261,7 @@
         <v>3</v>
       </c>
       <c r="K38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="b">
         <v>1</v>
@@ -4282,7 +4282,7 @@
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S38" t="b">
         <v>1</v>
@@ -4291,7 +4291,7 @@
         <v>2</v>
       </c>
       <c r="U38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" t="b">
         <v>1</v>
@@ -4312,7 +4312,7 @@
         <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC38" t="b">
         <v>1</v>
@@ -4321,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -4353,7 +4353,7 @@
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S39" t="b">
         <v>1</v>
@@ -4392,7 +4392,7 @@
         <v>3</v>
       </c>
       <c r="U39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" t="b">
         <v>1</v>
@@ -4413,7 +4413,7 @@
         <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC39" t="b">
         <v>0</v>
@@ -4454,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -4514,7 +4514,7 @@
         <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC40" t="b">
         <v>0</v>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -4555,7 +4555,7 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -4585,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S41" t="b">
         <v>1</v>
@@ -4594,7 +4594,7 @@
         <v>3</v>
       </c>
       <c r="U41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" t="b">
         <v>1</v>
@@ -4615,7 +4615,7 @@
         <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC41" t="b">
         <v>0</v>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -4656,7 +4656,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -4686,7 +4686,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S42" t="b">
         <v>1</v>
@@ -4695,7 +4695,7 @@
         <v>3</v>
       </c>
       <c r="U42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" t="b">
         <v>1</v>
@@ -4716,7 +4716,7 @@
         <v>1</v>
       </c>
       <c r="AB42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC42" t="b">
         <v>0</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC43" t="b">
         <v>0</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -4858,7 +4858,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S44" t="b">
         <v>1</v>
@@ -4897,7 +4897,7 @@
         <v>3</v>
       </c>
       <c r="U44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" t="b">
         <v>0</v>
@@ -4959,7 +4959,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -5019,7 +5019,7 @@
         <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC45" t="b">
         <v>0</v>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -5060,7 +5060,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S46" t="b">
         <v>1</v>
@@ -5099,7 +5099,7 @@
         <v>3</v>
       </c>
       <c r="U46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" t="b">
         <v>1</v>
@@ -5120,7 +5120,7 @@
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC46" t="b">
         <v>0</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -5173,10 +5173,10 @@
         <v>1</v>
       </c>
       <c r="L47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -5185,13 +5185,13 @@
         <v>0</v>
       </c>
       <c r="P47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="b">
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S47" t="b">
         <v>1</v>
@@ -5200,7 +5200,7 @@
         <v>3</v>
       </c>
       <c r="U47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" t="b">
         <v>1</v>
@@ -5221,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC47" t="b">
         <v>0</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -5262,7 +5262,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -5292,7 +5292,7 @@
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S48" t="b">
         <v>1</v>
@@ -5301,7 +5301,7 @@
         <v>3</v>
       </c>
       <c r="U48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" t="b">
         <v>1</v>
@@ -5322,7 +5322,7 @@
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC48" t="b">
         <v>0</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -5363,7 +5363,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S49" t="b">
         <v>1</v>
@@ -5402,7 +5402,7 @@
         <v>3</v>
       </c>
       <c r="U49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V49" t="b">
         <v>0</v>
@@ -5423,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC49" t="b">
         <v>0</v>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -5464,7 +5464,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -5494,7 +5494,7 @@
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S50" t="b">
         <v>1</v>
@@ -5503,7 +5503,7 @@
         <v>3</v>
       </c>
       <c r="U50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V50" t="b">
         <v>0</v>
@@ -5524,7 +5524,7 @@
         <v>1</v>
       </c>
       <c r="AB50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC50" t="b">
         <v>0</v>
@@ -5565,7 +5565,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -5625,7 +5625,7 @@
         <v>1</v>
       </c>
       <c r="AB51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC51" t="b">
         <v>0</v>
@@ -5959,11 +5959,11 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="b">
         <v>0</v>
@@ -5999,7 +5999,7 @@
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S55" t="b">
         <v>1</v>
@@ -6008,7 +6008,7 @@
         <v>3</v>
       </c>
       <c r="U55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V55" t="b">
         <v>0</v>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -6070,7 +6070,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I56" t="b">
         <v>0</v>
@@ -6100,7 +6100,7 @@
         <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S56" t="b">
         <v>1</v>
@@ -6109,7 +6109,7 @@
         <v>3</v>
       </c>
       <c r="U56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V56" t="b">
         <v>1</v>
@@ -6130,7 +6130,7 @@
         <v>1</v>
       </c>
       <c r="AB56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC56" t="b">
         <v>0</v>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -6171,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -6201,7 +6201,7 @@
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S57" t="b">
         <v>1</v>
@@ -6210,7 +6210,7 @@
         <v>3</v>
       </c>
       <c r="U57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V57" t="b">
         <v>1</v>
@@ -6231,7 +6231,7 @@
         <v>1</v>
       </c>
       <c r="AB57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC57" t="b">
         <v>0</v>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -6272,7 +6272,7 @@
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
@@ -6302,7 +6302,7 @@
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S58" t="b">
         <v>1</v>
@@ -6311,7 +6311,7 @@
         <v>3</v>
       </c>
       <c r="U58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V58" t="b">
         <v>1</v>
@@ -6332,7 +6332,7 @@
         <v>1</v>
       </c>
       <c r="AB58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC58" t="b">
         <v>0</v>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -6373,7 +6373,7 @@
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
@@ -6403,7 +6403,7 @@
         <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S59" t="b">
         <v>1</v>
@@ -6412,7 +6412,7 @@
         <v>3</v>
       </c>
       <c r="U59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V59" t="b">
         <v>1</v>
@@ -6433,7 +6433,7 @@
         <v>1</v>
       </c>
       <c r="AB59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC59" t="b">
         <v>0</v>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -6474,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60" t="b">
         <v>0</v>
@@ -6504,7 +6504,7 @@
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S60" t="b">
         <v>1</v>
@@ -6513,7 +6513,7 @@
         <v>3</v>
       </c>
       <c r="U60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V60" t="b">
         <v>1</v>
@@ -6534,7 +6534,7 @@
         <v>1</v>
       </c>
       <c r="AB60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC60" t="b">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -6635,7 +6635,7 @@
         <v>1</v>
       </c>
       <c r="AB61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC61" t="b">
         <v>0</v>
@@ -6666,17 +6666,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="b">
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I62" t="b">
         <v>1</v>
@@ -6685,7 +6685,7 @@
         <v>3</v>
       </c>
       <c r="K62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="b">
         <v>1</v>
@@ -6706,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S62" t="b">
         <v>1</v>
@@ -6715,7 +6715,7 @@
         <v>3</v>
       </c>
       <c r="U62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V62" t="b">
         <v>1</v>
@@ -6736,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="AB62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC62" t="b">
         <v>1</v>
@@ -6745,7 +6745,7 @@
         <v>3</v>
       </c>
       <c r="AE62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -6767,17 +6767,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="b">
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
@@ -6786,7 +6786,7 @@
         <v>3</v>
       </c>
       <c r="K63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -6807,7 +6807,7 @@
         <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S63" t="b">
         <v>1</v>
@@ -6816,7 +6816,7 @@
         <v>3</v>
       </c>
       <c r="U63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V63" t="b">
         <v>1</v>
@@ -6837,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="AB63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC63" t="b">
         <v>1</v>
@@ -6846,7 +6846,7 @@
         <v>3</v>
       </c>
       <c r="AE63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -6868,11 +6868,11 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="b">
         <v>0</v>
@@ -6908,7 +6908,7 @@
         <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S64" t="b">
         <v>1</v>
@@ -6917,7 +6917,7 @@
         <v>3</v>
       </c>
       <c r="U64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V64" t="b">
         <v>0</v>
@@ -6979,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>1</v>
       </c>
       <c r="AB65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC65" t="b">
         <v>0</v>
@@ -7070,11 +7070,11 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="b">
         <v>0</v>
@@ -7110,7 +7110,7 @@
         <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S66" t="b">
         <v>1</v>
@@ -7119,7 +7119,7 @@
         <v>3</v>
       </c>
       <c r="U66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V66" t="b">
         <v>0</v>
@@ -7181,7 +7181,7 @@
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
@@ -7241,7 +7241,7 @@
         <v>1</v>
       </c>
       <c r="AB67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC67" t="b">
         <v>0</v>
@@ -7342,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="AB68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC68" t="b">
         <v>0</v>
@@ -7383,7 +7383,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I69" t="b">
         <v>0</v>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -7484,7 +7484,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I70" t="b">
         <v>0</v>
@@ -7514,7 +7514,7 @@
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S70" t="b">
         <v>1</v>
@@ -7523,7 +7523,7 @@
         <v>3</v>
       </c>
       <c r="U70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V70" t="b">
         <v>1</v>
@@ -7544,7 +7544,7 @@
         <v>1</v>
       </c>
       <c r="AB70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC70" t="b">
         <v>0</v>
@@ -7575,17 +7575,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I71" t="b">
         <v>1</v>
@@ -7594,7 +7594,7 @@
         <v>3</v>
       </c>
       <c r="K71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="b">
         <v>1</v>
@@ -7645,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="AB71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC71" t="b">
         <v>1</v>
@@ -7654,7 +7654,7 @@
         <v>3</v>
       </c>
       <c r="AE71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -7676,11 +7676,11 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>VERIFIER_SURPLUS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="b">
         <v>0</v>
@@ -7716,7 +7716,7 @@
         <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S72" t="b">
         <v>1</v>
@@ -7725,7 +7725,7 @@
         <v>3</v>
       </c>
       <c r="U72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V72" t="b">
         <v>0</v>
@@ -7787,7 +7787,7 @@
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I73" t="b">
         <v>0</v>
@@ -7847,7 +7847,7 @@
         <v>1</v>
       </c>
       <c r="AB73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC73" t="b">
         <v>0</v>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -7888,7 +7888,7 @@
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I74" t="b">
         <v>0</v>
@@ -7918,7 +7918,7 @@
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S74" t="b">
         <v>1</v>
@@ -7927,7 +7927,7 @@
         <v>3</v>
       </c>
       <c r="U74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V74" t="b">
         <v>1</v>
@@ -7948,7 +7948,7 @@
         <v>1</v>
       </c>
       <c r="AB74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC74" t="b">
         <v>0</v>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -7989,7 +7989,7 @@
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I75" t="b">
         <v>0</v>
@@ -8019,7 +8019,7 @@
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S75" t="b">
         <v>1</v>
@@ -8028,7 +8028,7 @@
         <v>3</v>
       </c>
       <c r="U75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V75" t="b">
         <v>1</v>
@@ -8049,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="AB75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC75" t="b">
         <v>0</v>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -8090,7 +8090,7 @@
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I76" t="b">
         <v>0</v>
@@ -8120,7 +8120,7 @@
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S76" t="b">
         <v>1</v>
@@ -8129,7 +8129,7 @@
         <v>3</v>
       </c>
       <c r="U76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V76" t="b">
         <v>1</v>
@@ -8150,7 +8150,7 @@
         <v>1</v>
       </c>
       <c r="AB76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC76" t="b">
         <v>0</v>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -8191,7 +8191,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I77" t="b">
         <v>0</v>
@@ -8221,7 +8221,7 @@
         <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S77" t="b">
         <v>1</v>
@@ -8230,7 +8230,7 @@
         <v>3</v>
       </c>
       <c r="U77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V77" t="b">
         <v>1</v>
@@ -8251,7 +8251,7 @@
         <v>1</v>
       </c>
       <c r="AB77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC77" t="b">
         <v>0</v>
@@ -8292,7 +8292,7 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I78" t="b">
         <v>0</v>
@@ -8352,7 +8352,7 @@
         <v>1</v>
       </c>
       <c r="AB78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC78" t="b">
         <v>0</v>
@@ -8393,7 +8393,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I79" t="b">
         <v>0</v>
@@ -8453,7 +8453,7 @@
         <v>1</v>
       </c>
       <c r="AB79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC79" t="b">
         <v>0</v>
@@ -8494,7 +8494,7 @@
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I80" t="b">
         <v>0</v>
@@ -8554,7 +8554,7 @@
         <v>1</v>
       </c>
       <c r="AB80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC80" t="b">
         <v>0</v>
@@ -8595,7 +8595,7 @@
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I81" t="b">
         <v>0</v>
@@ -8655,7 +8655,7 @@
         <v>1</v>
       </c>
       <c r="AB81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC81" t="b">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I82" t="b">
         <v>0</v>
@@ -8756,7 +8756,7 @@
         <v>1</v>
       </c>
       <c r="AB82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC82" t="b">
         <v>0</v>
@@ -8797,7 +8797,7 @@
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I83" t="b">
         <v>0</v>
@@ -8857,7 +8857,7 @@
         <v>1</v>
       </c>
       <c r="AB83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC83" t="b">
         <v>0</v>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -8898,7 +8898,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I84" t="b">
         <v>0</v>
@@ -8928,7 +8928,7 @@
         <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S84" t="b">
         <v>1</v>
@@ -8937,7 +8937,7 @@
         <v>3</v>
       </c>
       <c r="U84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V84" t="b">
         <v>0</v>
@@ -8958,7 +8958,7 @@
         <v>1</v>
       </c>
       <c r="AB84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC84" t="b">
         <v>0</v>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -8999,7 +8999,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I85" t="b">
         <v>0</v>
@@ -9029,7 +9029,7 @@
         <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S85" t="b">
         <v>1</v>
@@ -9038,7 +9038,7 @@
         <v>3</v>
       </c>
       <c r="U85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V85" t="b">
         <v>0</v>
@@ -9059,7 +9059,7 @@
         <v>1</v>
       </c>
       <c r="AB85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC85" t="b">
         <v>0</v>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -9130,7 +9130,7 @@
         <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S86" t="b">
         <v>1</v>
@@ -9139,7 +9139,7 @@
         <v>3</v>
       </c>
       <c r="U86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V86" t="b">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="AB86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC86" t="b">
         <v>0</v>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -9504,7 +9504,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I90" t="b">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S90" t="b">
         <v>1</v>
@@ -9543,7 +9543,7 @@
         <v>3</v>
       </c>
       <c r="U90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V90" t="b">
         <v>1</v>
@@ -9564,7 +9564,7 @@
         <v>1</v>
       </c>
       <c r="AB90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC90" t="b">
         <v>0</v>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -9605,7 +9605,7 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I91" t="b">
         <v>0</v>
@@ -9635,7 +9635,7 @@
         <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S91" t="b">
         <v>1</v>
@@ -9644,7 +9644,7 @@
         <v>3</v>
       </c>
       <c r="U91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V91" t="b">
         <v>1</v>
@@ -9665,7 +9665,7 @@
         <v>1</v>
       </c>
       <c r="AB91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC91" t="b">
         <v>0</v>
@@ -9706,7 +9706,7 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I92" t="b">
         <v>0</v>
@@ -9766,7 +9766,7 @@
         <v>1</v>
       </c>
       <c r="AB92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC92" t="b">
         <v>0</v>
@@ -9807,7 +9807,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I93" t="b">
         <v>0</v>
@@ -9867,7 +9867,7 @@
         <v>1</v>
       </c>
       <c r="AB93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC93" t="b">
         <v>0</v>
@@ -9943,16 +9943,16 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="E2" t="n">
         <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>18.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="3">
@@ -9962,22 +9962,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E3" t="n">
         <v>36</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>30.4</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="4">
@@ -9993,16 +9993,16 @@
         <v>76</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="E4" t="n">
         <v>226</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>17.4</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="5">
@@ -10043,16 +10043,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>228</v>
       </c>
       <c r="E6" t="n">
         <v>36</v>
       </c>
       <c r="F6" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>17.4</v>
+        <v>30.4</v>
       </c>
     </row>
   </sheetData>
@@ -10066,7 +10066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10149,12 +10149,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kpimé Tomégbé</t>
+          <t>Kpimé ( Séva )</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kpime tomegbe</t>
+          <t>kpime (seva)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -10169,31 +10169,31 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -10202,12 +10202,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pittah</t>
+          <t>Korbongou</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pittah</t>
+          <t>korbongou</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10222,7 +10222,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -10234,10 +10234,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
         <v>3</v>
@@ -10246,7 +10246,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -10255,12 +10255,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dzogbékomé</t>
+          <t>Koudjoundè</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dzogbekome</t>
+          <t>koudjounde</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10275,13 +10275,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -10293,13 +10293,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -10308,12 +10308,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kabou(okpandoukpo)</t>
+          <t>Koudjouwdè</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kabou (okpandoukpo)</t>
+          <t>koudjouwde</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -10328,7 +10328,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -10340,10 +10340,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -10361,12 +10361,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kpimé Woumé</t>
+          <t>Kpadapé</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kpime woume</t>
+          <t>kpadape</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -10381,7 +10381,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -10393,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
@@ -10405,7 +10405,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -10414,12 +10414,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sevegan</t>
+          <t>Kparatao</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sevegan</t>
+          <t>kparatao</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -10434,7 +10434,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -10446,19 +10446,19 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -10467,12 +10467,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kpimé Séva</t>
+          <t>Kpawa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kpime seva</t>
+          <t>kpawa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10487,7 +10487,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -10511,7 +10511,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -10520,12 +10520,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kpimé (Woumé )</t>
+          <t>Tchitchao</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kpime (woume)</t>
+          <t>tchitchao</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10540,31 +10540,31 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -10573,12 +10573,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sanfatoute</t>
+          <t>Kpimé (Tomégbé)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sanfatoute</t>
+          <t>kpime (tomegbe)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -10593,31 +10593,31 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -10626,12 +10626,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Womé Cascade</t>
+          <t>Kpimé (Woumé )</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>wome cascade</t>
+          <t>kpime (woume)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10646,13 +10646,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10664,13 +10664,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -10679,12 +10679,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Akéi</t>
+          <t>Kpimé Séva</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>akei</t>
+          <t>kpime seva</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10699,7 +10699,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -10723,7 +10723,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -10732,12 +10732,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Womé Ville</t>
+          <t>Komah</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>wome ville</t>
+          <t>komah</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10752,7 +10752,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -10764,10 +10764,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>3</v>
@@ -10776,7 +10776,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -10785,12 +10785,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Womé Zongo</t>
+          <t>Kpimé Tomégbé</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wome zongo</t>
+          <t>kpime tomegbe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10838,12 +10838,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Koudjoundè</t>
+          <t>Kpodzi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>koudjounde</t>
+          <t>kpodzi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10858,7 +10858,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -10870,10 +10870,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>3</v>
@@ -10882,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -10891,17 +10891,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kpimé ( Séva )</t>
+          <t>Lama Feing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kpime (seva)</t>
+          <t>lama feing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -10911,31 +10911,31 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -10944,17 +10944,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kpodzi</t>
+          <t>Lama Tchamdè</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kpodzi</t>
+          <t>lama tchamde</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -10964,7 +10964,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
@@ -10988,7 +10988,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -10997,17 +10997,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lama Feing</t>
+          <t>Lama-tessi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lama feing</t>
+          <t>lama-tessi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D18" t="b">
@@ -11017,7 +11017,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -11029,7 +11029,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
         <v>3</v>
@@ -11041,7 +11041,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -11050,17 +11050,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lama Tchamdè</t>
+          <t>Lavié Apédomé</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lama tchamde</t>
+          <t>lavie apedome</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -11070,7 +11070,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -11094,7 +11094,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -11103,17 +11103,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lama-tessi</t>
+          <t>Tchamdè</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>lama-tessi</t>
+          <t>tchamde</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -11123,7 +11123,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -11135,7 +11135,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>3</v>
@@ -11147,7 +11147,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -11156,17 +11156,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lavié Apédomé</t>
+          <t>Pittah</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>lavie apedome</t>
+          <t>pittah</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -11176,7 +11176,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -11188,10 +11188,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -11200,7 +11200,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -11209,17 +11209,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kpawa</t>
+          <t>Sanfatoute</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>kpawa</t>
+          <t>sanfatoute</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -11229,7 +11229,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -11241,10 +11241,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -11253,7 +11253,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -11262,17 +11262,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mission tové</t>
+          <t>Tchamba</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mission tove</t>
+          <t>tchamba</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -11282,7 +11282,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -11294,7 +11294,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>3</v>
@@ -11306,7 +11306,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -11315,17 +11315,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kpimé (Tomégbé)</t>
+          <t>Sevegan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>kpime (tomegbe)</t>
+          <t>sevegan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -11335,7 +11335,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -11347,10 +11347,10 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -11359,7 +11359,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -11368,17 +11368,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Abobo</t>
+          <t>Kpimé Woumé</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>abobo</t>
+          <t>kpime woume</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -11388,7 +11388,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -11403,7 +11403,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -11412,7 +11412,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -11441,7 +11441,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -11453,7 +11453,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
         <v>3</v>
@@ -11465,7 +11465,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -11474,17 +11474,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Zongo 1</t>
+          <t>Katore</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>zongo 1</t>
+          <t>katore</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -11494,7 +11494,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
         <v>3</v>
@@ -11518,7 +11518,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -11527,17 +11527,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Zomayi</t>
+          <t>Kabou(okpandoukpo)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>zomayi</t>
+          <t>kabou (okpandoukpo)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -11547,31 +11547,31 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -11580,17 +11580,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Yade</t>
+          <t>Zomayi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yade</t>
+          <t>zomayi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -11600,7 +11600,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -11612,7 +11612,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
         <v>3</v>
@@ -11624,7 +11624,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -11633,17 +11633,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Womé (Zongo)</t>
+          <t>Akéi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wome (zongo)</t>
+          <t>akei</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -11653,31 +11653,31 @@
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -11686,17 +11686,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Womé( Ville)</t>
+          <t>Yade</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wome (ville)</t>
+          <t>yade</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -11706,31 +11706,31 @@
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -11739,17 +11739,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Womé ( Cascade )</t>
+          <t>Alibi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wome (cascade)</t>
+          <t>alibi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -11759,31 +11759,31 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -11792,17 +11792,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Wli</t>
+          <t>Womé Zongo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>wli</t>
+          <t>wome zongo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -11812,7 +11812,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -11827,7 +11827,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>3</v>
@@ -11836,7 +11836,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -11845,17 +11845,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tsévié dévé</t>
+          <t>Apéssito</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>tsevie deve</t>
+          <t>apessito</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -11865,7 +11865,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -11877,7 +11877,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
         <v>3</v>
@@ -11889,7 +11889,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -11898,17 +11898,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sevagan</t>
+          <t>Womé Ville</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sevagan</t>
+          <t>wome ville</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -11933,16 +11933,16 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -11951,17 +11951,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tsévié dalavémodji</t>
+          <t>Womé Cascade</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>tsevie dalavemodji</t>
+          <t>wome cascade</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -11971,7 +11971,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -11986,7 +11986,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>3</v>
@@ -11995,7 +11995,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -12004,17 +12004,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tovégan</t>
+          <t>Bassar ( kpankissi)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>tovegan</t>
+          <t>bassar (kpankissi)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D37" t="b">
@@ -12024,7 +12024,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -12036,7 +12036,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
         <v>3</v>
@@ -12048,7 +12048,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -12057,17 +12057,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tekpo</t>
+          <t>Womé (Zongo)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>tekpo</t>
+          <t>wome (zongo)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -12077,31 +12077,31 @@
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
         <v>3</v>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -12110,17 +12110,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tchitchao</t>
+          <t>Bitchabé</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>tchitchao</t>
+          <t>bitchabe</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -12130,7 +12130,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -12142,7 +12142,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
         <v>3</v>
@@ -12154,7 +12154,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -12163,17 +12163,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tchamdè</t>
+          <t>Bohou</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tchamde</t>
+          <t>bohou</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -12183,7 +12183,7 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -12195,7 +12195,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
         <v>3</v>
@@ -12207,7 +12207,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -12216,17 +12216,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tchamba</t>
+          <t>Campement</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>tchamba</t>
+          <t>campement</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -12236,7 +12236,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -12248,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
         <v>3</v>
@@ -12260,7 +12260,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -12269,17 +12269,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tchalo</t>
+          <t>Womé( Ville)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tchalo</t>
+          <t>wome (ville)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -12289,31 +12289,31 @@
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
         <v>3</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -12322,17 +12322,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Srikpui( Togblecopé)</t>
+          <t>Womé ( Cascade )</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>srikpui (togblecope)</t>
+          <t>wome (cascade)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -12342,31 +12342,31 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
         <v>3</v>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -12375,17 +12375,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tsévié blévé</t>
+          <t>Dimouri</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>tsevie bleve</t>
+          <t>dimouri</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D44" t="b">
@@ -12395,7 +12395,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -12407,7 +12407,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
         <v>3</v>
@@ -12419,7 +12419,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -12428,17 +12428,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kpadapé</t>
+          <t>Djidjolé</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kpadape</t>
+          <t>djidjole</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -12448,7 +12448,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -12460,7 +12460,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
         <v>3</v>
@@ -12472,7 +12472,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -12481,17 +12481,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kparatao</t>
+          <t>Doutikopé</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kparatao</t>
+          <t>doutikope</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -12501,7 +12501,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -12513,7 +12513,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
         <v>3</v>
@@ -12525,7 +12525,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -12534,17 +12534,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Koudjouwdè</t>
+          <t>Dzogbékomé</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>koudjouwde</t>
+          <t>dzogbekome</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -12554,7 +12554,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -12566,10 +12566,10 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -12587,17 +12587,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dimouri</t>
+          <t>Kabou (okpandoupo)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>dimouri</t>
+          <t>kabou (okpandoupo)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -12607,7 +12607,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -12619,7 +12619,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
         <v>3</v>
@@ -12631,7 +12631,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -12640,17 +12640,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dikamé</t>
+          <t>Tchalo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>dikame</t>
+          <t>tchalo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VERIFIER_MIXTE</t>
+          <t>IMPORTER_ESSAIS</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -12660,7 +12660,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -12672,19 +12672,19 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
         <v>3</v>
       </c>
       <c r="L49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -12693,12 +12693,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kovié</t>
+          <t>Wli</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>kovie</t>
+          <t>wli</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -12713,7 +12713,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -12737,7 +12737,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -12746,12 +12746,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Campement</t>
+          <t>Tekpo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>campement</t>
+          <t>tekpo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -12766,7 +12766,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -12778,7 +12778,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>3</v>
@@ -12790,7 +12790,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -12799,12 +12799,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bohou</t>
+          <t>Tsévié dévé</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bohou</t>
+          <t>tsevie deve</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -12819,7 +12819,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -12831,7 +12831,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>3</v>
@@ -12843,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -12852,12 +12852,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bitchabé</t>
+          <t>Tsévié dalavémodji</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bitchabe</t>
+          <t>tsevie dalavemodji</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -12872,7 +12872,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -12884,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>3</v>
@@ -12896,7 +12896,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -12905,12 +12905,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Belgique</t>
+          <t>Tsévié blévé</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>belgique</t>
+          <t>tsevie bleve</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -12925,7 +12925,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -12940,7 +12940,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L54" t="n">
         <v>3</v>
@@ -12949,7 +12949,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -12958,12 +12958,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bassar ( kpankissi)</t>
+          <t>Tovégan</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bassar (kpankissi)</t>
+          <t>tovegan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -12978,7 +12978,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -12990,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>3</v>
@@ -13002,7 +13002,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -13011,12 +13011,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Badja</t>
+          <t>Abobo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>badja</t>
+          <t>abobo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -13031,7 +13031,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -13055,7 +13055,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -13064,12 +13064,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Assahoun</t>
+          <t>Sevagan</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>assahoun</t>
+          <t>sevagan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -13084,7 +13084,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -13102,13 +13102,13 @@
         <v>3</v>
       </c>
       <c r="L57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -13117,12 +13117,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Apéssito</t>
+          <t>Adétikopé</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>apessito</t>
+          <t>adetikope</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -13137,7 +13137,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -13149,7 +13149,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>3</v>
@@ -13161,7 +13161,7 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -13170,12 +13170,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Apéhéme</t>
+          <t>Aképé</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>apeheme</t>
+          <t>akepe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -13190,7 +13190,7 @@
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -13214,7 +13214,7 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -13223,12 +13223,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alibi</t>
+          <t>Apéhéme</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>alibi</t>
+          <t>apeheme</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -13243,7 +13243,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -13255,7 +13255,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>3</v>
@@ -13267,7 +13267,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -13276,12 +13276,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Aképé</t>
+          <t>Assahoun</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>akepe</t>
+          <t>assahoun</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -13296,7 +13296,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -13320,7 +13320,7 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -13329,12 +13329,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Adétikopé</t>
+          <t>Badja</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>adetikope</t>
+          <t>badja</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -13349,7 +13349,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -13373,7 +13373,7 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -13382,12 +13382,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Djagblé</t>
+          <t>Belgique</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>djagble</t>
+          <t>belgique</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -13402,7 +13402,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
@@ -13426,7 +13426,7 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -13435,12 +13435,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Djidjolé</t>
+          <t>Dalavé</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>djidjole</t>
+          <t>dalave</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -13455,7 +13455,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -13467,7 +13467,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
         <v>3</v>
@@ -13479,7 +13479,7 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -13488,12 +13488,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dalavé</t>
+          <t>Srikpui( Togblecopé)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>dalave</t>
+          <t>srikpui (togblecope)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -13508,7 +13508,7 @@
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -13532,7 +13532,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -13541,12 +13541,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Zongo 2</t>
+          <t>Dikamé</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>zongo 2</t>
+          <t>dikame</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -13561,7 +13561,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -13585,7 +13585,7 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -13594,12 +13594,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Korbongou</t>
+          <t>Dzogbékopé</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>korbongou</t>
+          <t>dzogbekope</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -13614,7 +13614,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -13626,7 +13626,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>3</v>
@@ -13638,7 +13638,7 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -13647,12 +13647,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Doutikopé</t>
+          <t>Gbatopé</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>doutikope</t>
+          <t>gbatope</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -13667,7 +13667,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -13679,7 +13679,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
         <v>3</v>
@@ -13691,7 +13691,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -13700,12 +13700,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Dzogbékopé</t>
+          <t>Hahotoé</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>dzogbekope</t>
+          <t>hahotoe</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -13720,7 +13720,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -13744,7 +13744,7 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -13753,12 +13753,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Gbatopé</t>
+          <t>Kévé</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>gbatope</t>
+          <t>keve</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -13773,7 +13773,7 @@
         <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -13797,7 +13797,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -13806,12 +13806,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hahotoé</t>
+          <t>Kovié</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>hahotoe</t>
+          <t>kovie</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -13826,7 +13826,7 @@
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -13850,7 +13850,7 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -13859,12 +13859,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kabou (okpandoupo)</t>
+          <t>Zongo 1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>kabou (okpandoupo)</t>
+          <t>zongo 1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -13879,7 +13879,7 @@
         <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -13891,7 +13891,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>3</v>
@@ -13903,7 +13903,7 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -13912,12 +13912,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Komah</t>
+          <t>Mission tové</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>komah</t>
+          <t>mission tove</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -13932,7 +13932,7 @@
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -13944,7 +13944,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>3</v>
@@ -13956,7 +13956,7 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -13965,12 +13965,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kévé</t>
+          <t>Djagblé</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>keve</t>
+          <t>djagble</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -13985,7 +13985,7 @@
         <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -14009,7 +14009,7 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -14018,12 +14018,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Katore</t>
+          <t>Zongo 2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>katore</t>
+          <t>zongo 2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -14038,7 +14038,7 @@
         <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -14050,7 +14050,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>3</v>
@@ -14062,964 +14062,10 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Adjengré ( Pounpoun)</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>adjengre (pounpoun)</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D76" t="b">
-        <v>1</v>
-      </c>
-      <c r="E76" t="b">
-        <v>1</v>
-      </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="n">
-        <v>3</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Adjengré (Pounpouni)</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>adjengre (pounpouni)</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D77" t="b">
-        <v>1</v>
-      </c>
-      <c r="E77" t="b">
-        <v>1</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>3</v>
-      </c>
-      <c r="I77" t="n">
-        <v>3</v>
-      </c>
-      <c r="J77" t="n">
-        <v>1</v>
-      </c>
-      <c r="K77" t="n">
-        <v>3</v>
-      </c>
-      <c r="L77" t="n">
-        <v>3</v>
-      </c>
-      <c r="M77" t="n">
-        <v>3</v>
-      </c>
-      <c r="N77" t="n">
-        <v>1</v>
-      </c>
-      <c r="O77" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Agotivé</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>agotive</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D78" t="b">
-        <v>1</v>
-      </c>
-      <c r="E78" t="b">
-        <v>1</v>
-      </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="n">
-        <v>3</v>
-      </c>
-      <c r="H78" t="n">
-        <v>3</v>
-      </c>
-      <c r="I78" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" t="n">
-        <v>1</v>
-      </c>
-      <c r="K78" t="n">
-        <v>3</v>
-      </c>
-      <c r="L78" t="n">
-        <v>3</v>
-      </c>
-      <c r="M78" t="n">
-        <v>3</v>
-      </c>
-      <c r="N78" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Akié</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>akie</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D79" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" t="b">
-        <v>1</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="n">
-        <v>1</v>
-      </c>
-      <c r="K79" t="n">
-        <v>3</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Anié</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>anie</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D80" t="b">
-        <v>1</v>
-      </c>
-      <c r="E80" t="b">
-        <v>1</v>
-      </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" t="n">
-        <v>3</v>
-      </c>
-      <c r="H80" t="n">
-        <v>3</v>
-      </c>
-      <c r="I80" t="n">
-        <v>3</v>
-      </c>
-      <c r="J80" t="n">
-        <v>1</v>
-      </c>
-      <c r="K80" t="n">
-        <v>3</v>
-      </c>
-      <c r="L80" t="n">
-        <v>3</v>
-      </c>
-      <c r="M80" t="n">
-        <v>3</v>
-      </c>
-      <c r="N80" t="n">
-        <v>1</v>
-      </c>
-      <c r="O80" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Kaniamboua ( Bago )</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>kaniamboua (bago)</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D81" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" t="b">
-        <v>1</v>
-      </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" t="n">
-        <v>3</v>
-      </c>
-      <c r="H81" t="n">
-        <v>3</v>
-      </c>
-      <c r="I81" t="n">
-        <v>3</v>
-      </c>
-      <c r="J81" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" t="n">
-        <v>2</v>
-      </c>
-      <c r="L81" t="n">
-        <v>3</v>
-      </c>
-      <c r="M81" t="n">
-        <v>3</v>
-      </c>
-      <c r="N81" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Sanfatoule</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>sanfatoule</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D82" t="b">
-        <v>1</v>
-      </c>
-      <c r="E82" t="b">
-        <v>1</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" t="n">
-        <v>1</v>
-      </c>
-      <c r="K82" t="n">
-        <v>3</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Kamina Dakré</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>kamina dakre</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D83" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" t="b">
-        <v>1</v>
-      </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="n">
-        <v>3</v>
-      </c>
-      <c r="H83" t="n">
-        <v>3</v>
-      </c>
-      <c r="I83" t="n">
-        <v>3</v>
-      </c>
-      <c r="J83" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" t="n">
-        <v>3</v>
-      </c>
-      <c r="L83" t="n">
-        <v>3</v>
-      </c>
-      <c r="M83" t="n">
-        <v>3</v>
-      </c>
-      <c r="N83" t="n">
-        <v>1</v>
-      </c>
-      <c r="O83" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Pitiah</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>pitiah</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D84" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" t="b">
-        <v>1</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="n">
-        <v>1</v>
-      </c>
-      <c r="K84" t="n">
-        <v>3</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Badomé</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>badome</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D85" t="b">
-        <v>1</v>
-      </c>
-      <c r="E85" t="b">
-        <v>1</v>
-      </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" t="n">
-        <v>3</v>
-      </c>
-      <c r="H85" t="n">
-        <v>3</v>
-      </c>
-      <c r="I85" t="n">
-        <v>3</v>
-      </c>
-      <c r="J85" t="n">
-        <v>1</v>
-      </c>
-      <c r="K85" t="n">
-        <v>3</v>
-      </c>
-      <c r="L85" t="n">
-        <v>3</v>
-      </c>
-      <c r="M85" t="n">
-        <v>3</v>
-      </c>
-      <c r="N85" t="n">
-        <v>1</v>
-      </c>
-      <c r="O85" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Kpiné (Woumé)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>kpine (woume)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D86" t="b">
-        <v>1</v>
-      </c>
-      <c r="E86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" t="n">
-        <v>3</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Kadambara</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>kadambara</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D87" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" t="b">
-        <v>1</v>
-      </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" t="n">
-        <v>3</v>
-      </c>
-      <c r="H87" t="n">
-        <v>3</v>
-      </c>
-      <c r="I87" t="n">
-        <v>3</v>
-      </c>
-      <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" t="n">
-        <v>3</v>
-      </c>
-      <c r="L87" t="n">
-        <v>3</v>
-      </c>
-      <c r="M87" t="n">
-        <v>3</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Sotouboua (Soudè)</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>sotouboua (soude)</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D88" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" t="b">
-        <v>1</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" t="n">
-        <v>3</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Sotouboua ( Sondè )</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>sotouboua (sonde)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D89" t="b">
-        <v>1</v>
-      </c>
-      <c r="E89" t="b">
-        <v>1</v>
-      </c>
-      <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" t="n">
-        <v>3</v>
-      </c>
-      <c r="H89" t="n">
-        <v>3</v>
-      </c>
-      <c r="I89" t="n">
-        <v>3</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>3</v>
-      </c>
-      <c r="M89" t="n">
-        <v>3</v>
-      </c>
-      <c r="N89" t="n">
-        <v>1</v>
-      </c>
-      <c r="O89" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Nyamassila</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>nyamassila</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D90" t="b">
-        <v>1</v>
-      </c>
-      <c r="E90" t="b">
-        <v>1</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="n">
-        <v>3</v>
-      </c>
-      <c r="H90" t="n">
-        <v>3</v>
-      </c>
-      <c r="I90" t="n">
-        <v>3</v>
-      </c>
-      <c r="J90" t="n">
-        <v>1</v>
-      </c>
-      <c r="K90" t="n">
-        <v>3</v>
-      </c>
-      <c r="L90" t="n">
-        <v>3</v>
-      </c>
-      <c r="M90" t="n">
-        <v>3</v>
-      </c>
-      <c r="N90" t="n">
-        <v>1</v>
-      </c>
-      <c r="O90" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Ountivou</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>ountivou</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D91" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" t="b">
-        <v>1</v>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="n">
-        <v>3</v>
-      </c>
-      <c r="H91" t="n">
-        <v>3</v>
-      </c>
-      <c r="I91" t="n">
-        <v>3</v>
-      </c>
-      <c r="J91" t="n">
-        <v>1</v>
-      </c>
-      <c r="K91" t="n">
-        <v>3</v>
-      </c>
-      <c r="L91" t="n">
-        <v>3</v>
-      </c>
-      <c r="M91" t="n">
-        <v>3</v>
-      </c>
-      <c r="N91" t="n">
-        <v>1</v>
-      </c>
-      <c r="O91" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Apéyéyémé</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>apeyeyeme</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D92" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" t="b">
-        <v>1</v>
-      </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" t="n">
-        <v>3</v>
-      </c>
-      <c r="H92" t="n">
-        <v>3</v>
-      </c>
-      <c r="I92" t="n">
-        <v>3</v>
-      </c>
-      <c r="J92" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" t="n">
-        <v>3</v>
-      </c>
-      <c r="L92" t="n">
-        <v>3</v>
-      </c>
-      <c r="M92" t="n">
-        <v>3</v>
-      </c>
-      <c r="N92" t="n">
-        <v>1</v>
-      </c>
-      <c r="O92" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Kamina Barrage</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>kamina barrage</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>VERIFIER_SURPLUS</t>
-        </is>
-      </c>
-      <c r="D93" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" t="b">
-        <v>1</v>
-      </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" t="n">
-        <v>3</v>
-      </c>
-      <c r="H93" t="n">
-        <v>3</v>
-      </c>
-      <c r="I93" t="n">
-        <v>3</v>
-      </c>
-      <c r="J93" t="n">
-        <v>1</v>
-      </c>
-      <c r="K93" t="n">
-        <v>3</v>
-      </c>
-      <c r="L93" t="n">
-        <v>3</v>
-      </c>
-      <c r="M93" t="n">
-        <v>3</v>
-      </c>
-      <c r="N93" t="n">
-        <v>1</v>
-      </c>
-      <c r="O93" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
